--- a/demo_data/patients.xlsx
+++ b/demo_data/patients.xlsx
@@ -527,11 +527,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sunita Kumar</t>
+          <t>Amit Shah</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -540,79 +540,79 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1984-07-10</t>
+          <t>1983-11-09</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+91 9288106614</t>
+          <t>+91 9788852445</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>sunita.kumar@email.com</t>
+          <t>amit.shah@email.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>40, Brigade Road, Bengaluru</t>
+          <t>404, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AB-</t>
+          <t>O+</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Schizophrenia</t>
+          <t>Osteoarthritis</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>91-7278-4682-7455-4915</t>
+          <t>91-4987-3433-9096-9938</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Anita Shah</t>
+          <t>Rajesh Shah</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>+91 9711000268</t>
+          <t>+91 9207284717</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>POL-792294</t>
+          <t>POL-682281</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="3">
@@ -623,75 +623,75 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anil Verma</t>
+          <t>Amit Pillai</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1981-03-20</t>
+          <t>1958-07-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+91 9621912893</t>
+          <t>+91 9975153379</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>anil.verma@email.com</t>
+          <t>amit.pillai@email.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>434, Jayanagar, Bengaluru</t>
+          <t>178, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O-</t>
+          <t>O+</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Type 2 Diabetes</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>91-5446-2555-5665-4045</t>
+          <t>91-5681-9050-2440-6048</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Pooja Reddy</t>
+          <t>Pooja Kapoor</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>+91 9195673903</t>
+          <t>+91 9204685472</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="Q3" t="b">
@@ -704,11 +704,11 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>POL-312265</t>
+          <t>POL-902176</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>750000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="4">
@@ -719,88 +719,88 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rajesh Patel</t>
+          <t>Anil Mehta</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1959-12-01</t>
+          <t>1998-05-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+91 9813207325</t>
+          <t>+91 9634535093</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rajesh.patel@email.com</t>
+          <t>anil.mehta@email.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>414, Residency Road, Bengaluru</t>
+          <t>356, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>O-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Breast Cancer</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>91-7619-9541-3819-9589</t>
+          <t>91-5771-4017-6593-6888</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Sanjay Pillai</t>
+          <t>Rahul Agarwal</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>+91 9619953716</t>
+          <t>+91 9207743928</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="Q4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>POL-566341</t>
+          <t>POL-385374</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -815,11 +815,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pooja Dutta</t>
+          <t>Amit Shah</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -828,62 +828,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1977-03-13</t>
+          <t>2006-06-09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+91 9973065910</t>
+          <t>+91 9317472108</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pooja.dutta@email.com</t>
+          <t>amit.shah@email.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>279, Residency Road, Bengaluru</t>
+          <t>95, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AB+</t>
+          <t>AB-</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>91-7673-9993-9328-2452</t>
+          <t>91-6118-2698-5175-3414</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Arjun Pillai</t>
+          <t>Vikram Gupta</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>+91 9282183006</t>
+          <t>+91 9233935366</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="Q5" t="b">
@@ -891,16 +891,16 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Star Health</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>POL-570705</t>
+          <t>POL-564607</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="6">
@@ -911,92 +911,92 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rajesh Malhotra</t>
+          <t>Kiran Singh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1997-07-30</t>
+          <t>1971-04-17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+91 9146906737</t>
+          <t>+91 9943602394</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>rajesh.malhotra@email.com</t>
+          <t>kiran.singh@email.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>102, MG Road, Bengaluru</t>
+          <t>453, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>AB-</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>91-3646-6678-3665-2513</t>
+          <t>91-2805-1258-5432-1368</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Kiran Malhotra</t>
+          <t>Vikram Bose</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>+91 9985324487</t>
+          <t>+91 9924159009</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="Q6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>POL-134763</t>
+          <t>POL-628777</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="7">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arjun Pillai</t>
+          <t>Amit Malhotra</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1020,57 +1020,57 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1981-04-17</t>
+          <t>1974-02-28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+91 9724939571</t>
+          <t>+91 9310851322</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>arjun.pillai@email.com</t>
+          <t>amit.malhotra@email.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>87, Brigade Road, Bengaluru</t>
+          <t>200, Jayanagar, Bengaluru</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>AB-</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>91-2234-8195-9293-8080</t>
+          <t>91-4101-3191-1923-7765</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Kavita Singh</t>
+          <t>Arjun Gupta</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>+91 9112858011</t>
+          <t>+91 9812473702</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1083,16 +1083,16 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>POL-278592</t>
+          <t>POL-751654</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="8">
@@ -1103,11 +1103,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meena Reddy</t>
+          <t>Manish Joshi</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1116,62 +1116,62 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2006-03-19</t>
+          <t>2002-12-26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+91 9409504716</t>
+          <t>+91 9278787198</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>meena.reddy@email.com</t>
+          <t>manish.joshi@email.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>422, Brigade Road, Bengaluru</t>
+          <t>46, Jayanagar, Bengaluru</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>O-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Breast Cancer</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>91-5908-5141-3738-6656</t>
+          <t>91-9814-6718-1089-1838</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Anil Joshi</t>
+          <t>Kiran Iyer</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>+91 9506839494</t>
+          <t>+91 9979294202</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="Q8" t="b">
@@ -1179,16 +1179,16 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Bajaj Allianz</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>POL-506272</t>
+          <t>POL-608489</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="9">
@@ -1199,11 +1199,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arjun Rao</t>
+          <t>Meena Iyer</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1212,66 +1212,66 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1977-06-08</t>
+          <t>1973-10-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+91 9902164103</t>
+          <t>+91 9673312312</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>arjun.rao@email.com</t>
+          <t>meena.iyer@email.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>88, Jayanagar, Bengaluru</t>
+          <t>156, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AB+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hypothyroidism</t>
+          <t>CKD Stage 3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Dr. Sunita Sharma</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>91-7170-2224-3090-3649</t>
+          <t>91-9819-8599-6067-6151</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Kavita Gupta</t>
+          <t>Kavita Mehta</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>+91 9823946135</t>
+          <t>+91 9351858873</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>English</t>
         </is>
       </c>
       <c r="Q9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>POL-598856</t>
+          <t>POL-711954</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1295,35 +1295,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vikram Kumar</t>
+          <t>Anita Kapoor</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1961-11-25</t>
+          <t>1999-12-02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+91 9313044772</t>
+          <t>+91 9142269873</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>vikram.kumar@email.com</t>
+          <t>anita.kapoor@email.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>283, Residency Road, Bengaluru</t>
+          <t>463, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1333,37 +1333,37 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Type 2 Diabetes</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>91-6395-5583-5375-7716</t>
+          <t>91-7795-9419-6397-3086</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Manish Shah</t>
+          <t>Anil Rao</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>+91 9887432548</t>
+          <t>+91 9273269433</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>English</t>
         </is>
       </c>
       <c r="Q10" t="b">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Star Health</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>POL-222072</t>
+          <t>POL-561962</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1391,40 +1391,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rajesh Agarwal</t>
+          <t>Sanjay Verma</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2004-11-11</t>
+          <t>2003-10-30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+91 9794582311</t>
+          <t>+91 9144210757</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rajesh.agarwal@email.com</t>
+          <t>sanjay.verma@email.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>226, Jayanagar, Bengaluru</t>
+          <t>185, Jayanagar, Bengaluru</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>AB+</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1434,27 +1434,27 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>91-3057-8307-9091-9618</t>
+          <t>91-3216-3923-4365-6938</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Manish Kapoor</t>
+          <t>Arjun Joshi</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>+91 9148081576</t>
+          <t>+91 9877193591</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1467,16 +1467,16 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>POL-203360</t>
+          <t>POL-232893</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>300000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="12">
@@ -1487,75 +1487,75 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Usha Pillai</t>
+          <t>Pooja Dutta</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1963-11-19</t>
+          <t>2008-05-08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+91 9576166512</t>
+          <t>+91 9561166539</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>usha.pillai@email.com</t>
+          <t>pooja.dutta@email.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>119, Jayanagar, Bengaluru</t>
+          <t>68, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Type 2 Diabetes</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>91-3720-7179-4927-6840</t>
+          <t>91-2913-6690-3835-8607</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Suresh Reddy</t>
+          <t>Rekha Iyer</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>+91 9931979755</t>
+          <t>+91 9532294164</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>English</t>
         </is>
       </c>
       <c r="Q12" t="b">
@@ -1563,16 +1563,16 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>POL-368704</t>
+          <t>POL-747018</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="13">
@@ -1583,11 +1583,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pooja Gupta</t>
+          <t>Kavita Gupta</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1596,62 +1596,62 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2002-06-22</t>
+          <t>2004-07-23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+91 9911057342</t>
+          <t>+91 9727703234</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>pooja.gupta@email.com</t>
+          <t>kavita.gupta@email.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>203, Residency Road, Bengaluru</t>
+          <t>278, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>CKD Stage 3</t>
+          <t>Breast Cancer</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>91-4931-7756-4903-3239</t>
+          <t>91-5332-5460-5740-2210</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Manish Iyer</t>
+          <t>Arjun Bose</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>+91 9523148606</t>
+          <t>+91 9881451601</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="Q13" t="b">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Star Health</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>POL-444799</t>
+          <t>POL-685863</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1679,11 +1679,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anil Malhotra</t>
+          <t>Usha Agarwal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1692,32 +1692,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1987-01-11</t>
+          <t>1983-03-25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+91 9430121892</t>
+          <t>+91 9150844519</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>anil.malhotra@email.com</t>
+          <t>usha.agarwal@email.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>122, Jayanagar, Bengaluru</t>
+          <t>5, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O-</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Breast Cancer</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1727,22 +1727,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>91-5641-7119-1693-1447</t>
+          <t>91-9109-6256-8590-6382</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Anita Agarwal</t>
+          <t>Meena Rao</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>+91 9857937145</t>
+          <t>+91 9738690255</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1755,16 +1755,16 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>POL-662800</t>
+          <t>POL-698268</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="15">
@@ -1775,11 +1775,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sunita Joshi</t>
+          <t>Kiran Shah</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1788,62 +1788,62 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1997-08-09</t>
+          <t>1970-05-21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+91 9557612676</t>
+          <t>+91 9510261931</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>sunita.joshi@email.com</t>
+          <t>kiran.shah@email.com</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>39, Residency Road, Bengaluru</t>
+          <t>406, Jayanagar, Bengaluru</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Type 2 Diabetes</t>
+          <t>Osteoarthritis</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>91-9493-9422-2659-6765</t>
+          <t>91-5302-6750-7756-8169</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Kavita Agarwal</t>
+          <t>Pooja Chatterjee</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>+91 9461054500</t>
+          <t>+91 9829474525</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="Q15" t="b">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>POL-509509</t>
+          <t>POL-773794</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1871,75 +1871,75 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rekha Kumar</t>
+          <t>Sanjay Patel</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2007-12-27</t>
+          <t>1995-01-26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+91 9771226172</t>
+          <t>+91 9590820358</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>rekha.kumar@email.com</t>
+          <t>sanjay.patel@email.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>359, Brigade Road, Bengaluru</t>
+          <t>129, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Breast Cancer</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Dr. Anita Singh</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>91-2242-3269-9823-3747</t>
+          <t>91-5260-7227-8543-5745</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Sanjay Singh</t>
+          <t>Anil Malhotra</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>+91 9634736266</t>
+          <t>+91 9203018259</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="Q16" t="b">
@@ -1947,16 +1947,16 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>POL-144631</t>
+          <t>POL-548640</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="17">
@@ -1967,11 +1967,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anita Pillai</t>
+          <t>Manish Iyer</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1980,57 +1980,57 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2001-05-25</t>
+          <t>2004-01-04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+91 9349058465</t>
+          <t>+91 9566632885</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>anita.pillai@email.com</t>
+          <t>manish.iyer@email.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>95, Brigade Road, Bengaluru</t>
+          <t>158, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O-</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>CKD Stage 3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>91-3492-9632-8092-8499</t>
+          <t>91-8900-1376-5197-4666</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Rajesh Chatterjee</t>
+          <t>Usha Rao</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>+91 9148890491</t>
+          <t>+91 9246121461</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2048,11 +2048,11 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>POL-869718</t>
+          <t>POL-450799</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="18">
@@ -2063,70 +2063,70 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Meena Rao</t>
+          <t>Rahul Joshi</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2004-04-02</t>
+          <t>1994-12-09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+91 9147250682</t>
+          <t>+91 9269632279</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>meena.rao@email.com</t>
+          <t>rahul.joshi@email.com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>347, MG Road, Bengaluru</t>
+          <t>129, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O-</t>
+          <t>AB+</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Schizophrenia</t>
+          <t>CKD Stage 3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>91-2487-1354-7465-3136</t>
+          <t>91-5654-2908-2895-1790</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Arjun Iyer</t>
+          <t>Amit Dutta</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>+91 9886403674</t>
+          <t>+91 9217237506</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2135,20 +2135,20 @@
         </is>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>POL-231793</t>
+          <t>POL-759546</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="19">
@@ -2159,75 +2159,75 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rahul Kapoor</t>
+          <t>Priya Iyer</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2002-05-03</t>
+          <t>2006-04-10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+91 9781906673</t>
+          <t>+91 9262638285</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>rahul.kapoor@email.com</t>
+          <t>priya.iyer@email.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>302, Residency Road, Bengaluru</t>
+          <t>62, Jayanagar, Bengaluru</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>O-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>91-5969-4770-7866-4829</t>
+          <t>91-6771-9621-4487-6264</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Sunita Kumar</t>
+          <t>Pooja Rao</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>+91 9985747693</t>
+          <t>+91 9929767462</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="Q19" t="b">
@@ -2235,16 +2235,16 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Star Health</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>POL-529309</t>
+          <t>POL-418579</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>300000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="20">
@@ -2255,11 +2255,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rekha Malhotra</t>
+          <t>Priya Rao</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2268,62 +2268,62 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1977-07-15</t>
+          <t>1980-02-23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+91 9793364340</t>
+          <t>+91 9274850402</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rekha.malhotra@email.com</t>
+          <t>priya.rao@email.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>371, Jayanagar, Bengaluru</t>
+          <t>58, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AB+</t>
+          <t>AB-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>91-9349-7835-4712-2341</t>
+          <t>91-2219-7900-7248-7538</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Priya Agarwal</t>
+          <t>Rekha Verma</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>+91 9220054229</t>
+          <t>+91 9155488210</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="Q20" t="b">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>POL-586757</t>
+          <t>POL-118568</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2351,88 +2351,88 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nisha Bose</t>
+          <t>Priya Agarwal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2005-10-25</t>
+          <t>2002-09-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+91 9859537415</t>
+          <t>+91 9765855813</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>nisha.bose@email.com</t>
+          <t>priya.agarwal@email.com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>472, Brigade Road, Bengaluru</t>
+          <t>364, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CKD Stage 3</t>
+          <t>Osteoarthritis</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>91-5786-8414-7883-7831</t>
+          <t>91-1402-9408-9534-1072</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Arjun Pillai</t>
+          <t>Kavita Sharma</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>+91 9375029125</t>
+          <t>+91 9690414489</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="Q21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>POL-158831</t>
+          <t>POL-887410</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2447,70 +2447,70 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nisha Agarwal</t>
+          <t>Anil Gupta</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1988-01-29</t>
+          <t>1980-07-03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+91 9796242074</t>
+          <t>+91 9895467835</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>nisha.agarwal@email.com</t>
+          <t>anil.gupta@email.com</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>366, MG Road, Bengaluru</t>
+          <t>146, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O+</t>
+          <t>B-</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Schizophrenia</t>
+          <t>Breast Cancer</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>91-4634-6365-8515-8783</t>
+          <t>91-4124-8659-3273-1920</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Manish Gupta</t>
+          <t>Rajesh Verma</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>+91 9787076378</t>
+          <t>+91 9364190472</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2523,16 +2523,16 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>POL-493704</t>
+          <t>POL-437659</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="23">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sanjay Rao</t>
+          <t>Anita Agarwal</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2556,62 +2556,62 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1965-09-18</t>
+          <t>1995-03-28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+91 9204374172</t>
+          <t>+91 9585009813</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>sanjay.rao@email.com</t>
+          <t>anita.agarwal@email.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>142, Jayanagar, Bengaluru</t>
+          <t>41, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>O+</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Osteoarthritis</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>91-1525-5299-5821-3126</t>
+          <t>91-4685-1908-7786-8304</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Anita Dutta</t>
+          <t>Sanjay Nair</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>+91 9793299619</t>
+          <t>+91 9187901851</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="Q23" t="b">
@@ -2619,16 +2619,16 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Star Health</t>
+          <t>None</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>POL-776680</t>
+          <t>POL-707839</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="24">
@@ -2639,11 +2639,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deepa Malhotra</t>
+          <t>Rekha Singh</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2652,75 +2652,75 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2004-07-17</t>
+          <t>1963-03-21</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+91 9532644597</t>
+          <t>+91 9545052281</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>deepa.malhotra@email.com</t>
+          <t>rekha.singh@email.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17, Jayanagar, Bengaluru</t>
+          <t>377, Brigade Road, Bengaluru</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Breast Cancer</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>91-3963-4856-9046-2698</t>
+          <t>91-6666-4809-6925-1732</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Anita Singh</t>
+          <t>Deepa Singh</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>+91 9815734612</t>
+          <t>+91 9461122419</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>HDFC ERGO</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>POL-969844</t>
+          <t>POL-184888</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2735,45 +2735,45 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pooja Nair</t>
+          <t>Rekha Pillai</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1990-07-09</t>
+          <t>2003-08-15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+91 9647560253</t>
+          <t>+91 9524287393</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>pooja.nair@email.com</t>
+          <t>rekha.pillai@email.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>438, MG Road, Bengaluru</t>
+          <t>115, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AB+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2783,31 +2783,31 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>91-8422-1139-8693-3176</t>
+          <t>91-9574-3470-3204-7009</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Kavita Rao</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>+91 9815642500</t>
+          <t>+91 9603691928</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>English</t>
         </is>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2816,11 +2816,11 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>POL-397402</t>
+          <t>POL-363408</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="26">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sanjay Pillai</t>
+          <t>Rajesh Joshi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2844,62 +2844,62 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1965-09-07</t>
+          <t>2004-10-24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+91 9303155524</t>
+          <t>+91 9527592018</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>sanjay.pillai@email.com</t>
+          <t>rajesh.joshi@email.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>249, Residency Road, Bengaluru</t>
+          <t>426, Residency Road, Bengaluru</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>B-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Osteoarthritis</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>91-7477-8058-5549-4348</t>
+          <t>91-4899-6237-5470-9546</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Deepa Patel</t>
+          <t>Suresh Gupta</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>+91 9638422062</t>
+          <t>+91 9736737461</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="Q26" t="b">
@@ -2912,11 +2912,11 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>POL-881120</t>
+          <t>POL-933424</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
   </sheetData>
@@ -2963,16 +2963,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>POL-792294</t>
+          <t>POL-682281</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="3">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>POL-312265</t>
+          <t>POL-902176</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>750000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="4">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>POL-566341</t>
+          <t>POL-385374</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3023,16 +3023,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Star Health</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>POL-570705</t>
+          <t>POL-564607</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="6">
@@ -3043,16 +3043,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>POL-134763</t>
+          <t>POL-628777</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="7">
@@ -3063,16 +3063,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>POL-278592</t>
+          <t>POL-751654</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="8">
@@ -3083,16 +3083,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bajaj Allianz</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>POL-506272</t>
+          <t>POL-608489</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="9">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>POL-598856</t>
+          <t>POL-711954</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Star Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>POL-222072</t>
+          <t>POL-561962</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3143,16 +3143,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>POL-203360</t>
+          <t>POL-232893</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>300000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="12">
@@ -3163,16 +3163,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>POL-368704</t>
+          <t>POL-747018</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="13">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Star Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>POL-444799</t>
+          <t>POL-685863</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -3203,16 +3203,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>POL-662800</t>
+          <t>POL-698268</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="15">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>POL-509509</t>
+          <t>POL-773794</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3243,16 +3243,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>POL-144631</t>
+          <t>POL-548640</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="17">
@@ -3268,11 +3268,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>POL-869718</t>
+          <t>POL-450799</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="18">
@@ -3283,16 +3283,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>POL-231793</t>
+          <t>POL-759546</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1000000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="19">
@@ -3303,16 +3303,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Star Health</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>POL-529309</t>
+          <t>POL-418579</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>300000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="20">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>POL-586757</t>
+          <t>POL-118568</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HDFC ERGO</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>POL-158831</t>
+          <t>POL-887410</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3363,16 +3363,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>Bajaj Allianz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>POL-493704</t>
+          <t>POL-437659</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="23">
@@ -3383,16 +3383,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Star Health</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>POL-776680</t>
+          <t>POL-707839</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="24">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>HDFC ERGO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>POL-969844</t>
+          <t>POL-184888</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3428,11 +3428,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>POL-397402</t>
+          <t>POL-363408</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="26">
@@ -3448,11 +3448,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>POL-881120</t>
+          <t>POL-933424</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
   </sheetData>
